--- a/テスト仕様書_PhoneLog_最新版.xlsx
+++ b/テスト仕様書_PhoneLog_最新版.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALMEIDA RAPHAEL\Documents\almeida\java\worstation_ij\phonelog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BCC834-9633-47D8-B2A2-60714224B6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB87F10-FE66-4AEB-9663-A501EF2CF1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト仕様書" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="210">
   <si>
     <t>No</t>
   </si>
@@ -808,6 +821,14 @@
   </si>
   <si>
     <t>画面確認・DB確認</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>同名ユーザーあり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なし</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2089,7 +2110,9 @@
       <c r="C45" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D45" s="2"/>
+      <c r="D45" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E45" s="2" t="s">
         <v>13</v>
       </c>
@@ -2107,7 +2130,9 @@
       <c r="C46" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D46" s="2"/>
+      <c r="D46" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E46" s="2" t="s">
         <v>13</v>
       </c>
@@ -2125,7 +2150,9 @@
       <c r="C47" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D47" s="2"/>
+      <c r="D47" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E47" s="2" t="s">
         <v>13</v>
       </c>
@@ -2143,7 +2170,9 @@
       <c r="C48" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D48" s="2"/>
+      <c r="D48" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E48" s="2" t="s">
         <v>13</v>
       </c>
@@ -2161,7 +2190,9 @@
       <c r="C49" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D49" s="2"/>
+      <c r="D49" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="E49" s="2" t="s">
         <v>199</v>
       </c>
